--- a/artifacts/commercial-price-list-2026-08-05/TINDA-Каталог продукции.xlsx
+++ b/artifacts/commercial-price-list-2026-08-05/TINDA-Каталог продукции.xlsx
@@ -15,14 +15,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Рычал-Су" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adrenaline Rush" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Viko" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ГК ПД «Бавария»" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ООО ВПБЗ «Дарьял»" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ООО «Константа-7»" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ООО «ИРИБ»" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Barbican" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KINZA" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ГК ПД «Бавария»" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ООО ВПБЗ «Дарьял»" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ООО «Константа-7»" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ООО «ИРИБ»" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Титул'!$A$1:$K$28</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -523,6 +523,650 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -780,6 +1424,576 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -2831,762 +4045,6 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>12</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>13</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="12" name="Image 12" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>15</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="13" name="Image 13" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>20</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="20" name="Image 20" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>23</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="21" name="Image 21" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>24</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="22" name="Image 22" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>25</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="23" name="Image 23" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>26</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="24" name="Image 24" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="25" name="Image 25" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>28</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="26" name="Image 26" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>29</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="27" name="Image 27" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>30</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>31</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="30" name="Image 30" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>33</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="31" name="Image 31" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>34</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="32" name="Image 32" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="33" name="Image 33" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="34" name="Image 34" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -3775,62 +4233,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -4151,37 +4553,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData>
-    <row r="1" ht="18" customHeight="1"/>
-    <row r="2" ht="18" customHeight="1"/>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1"/>
-    <row r="5" ht="18" customHeight="1"/>
-    <row r="6" ht="18" customHeight="1"/>
-    <row r="7" ht="18" customHeight="1"/>
-    <row r="8" ht="18" customHeight="1"/>
-    <row r="9" ht="18" customHeight="1"/>
-    <row r="10" ht="18" customHeight="1"/>
-    <row r="11" ht="18" customHeight="1"/>
-    <row r="12" ht="18" customHeight="1"/>
-    <row r="13" ht="18" customHeight="1"/>
-    <row r="14" ht="18" customHeight="1"/>
-    <row r="15" ht="18" customHeight="1"/>
-    <row r="16" ht="18" customHeight="1"/>
-    <row r="17" ht="18" customHeight="1"/>
-    <row r="18" ht="18" customHeight="1"/>
-    <row r="19" ht="18" customHeight="1"/>
-    <row r="20" ht="18" customHeight="1"/>
-    <row r="21" ht="18" customHeight="1"/>
-    <row r="22" ht="18" customHeight="1"/>
-    <row r="23" ht="18" customHeight="1"/>
-    <row r="24" ht="18" customHeight="1"/>
-    <row r="25" ht="18" customHeight="1"/>
-    <row r="26" ht="18" customHeight="1"/>
-    <row r="27" ht="18" customHeight="1"/>
-    <row r="28" ht="18" customHeight="1"/>
-    <row r="29" ht="18" customHeight="1"/>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4192,7 +4564,1774 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>KINZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Фото</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Производитель</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Вкус</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Объём</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Тара</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Описание</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Цена</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="96" customHeight="1">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный KINZA ж/б 320мл Лимон</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>KINZA</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Лимон</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>320 мл</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>банка</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>KINZA Лимон — газированный безалкогольный напиток в жестяной банке 320 мл.</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="96" customHeight="1">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный KINZA ж/б 320мл Черная смородина</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>KINZA</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Черная смородина</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>320 мл</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>банка</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>KINZA Черная смородина — газированный безалкогольный напиток в жестяной банке 320 мл.</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="96" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный KINZA кола ZERO ж/б 320мл</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>KINZA</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>кола ZERO</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>320 мл</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>банка</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>KINZA кола ZERO — газированный безалкогольный напиток в жестяной банке 320 мл.</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="96" customHeight="1">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный KINZA кола гранат ж/б 320мл</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>KINZA</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>кола гранат</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>320 мл</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>банка</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>KINZA кола гранат — газированный безалкогольный напиток в жестяной банке 320 мл.</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="96" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный KINZA кола ж/б 320мл</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>KINZA</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>кола</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>320 мл</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>банка</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>KINZA кола — газированный безалкогольный напиток в жестяной банке 320 мл.</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="96" customHeight="1">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный KINZA оранж ж/б 320мл</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>KINZA</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>оранж</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>320 мл</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>банка</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>KINZA оранж — газированный безалкогольный напиток в жестяной банке 320 мл.</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="96" customHeight="1">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный KINZA цитрус ж/б 320мл</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>KINZA</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>цитрус</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>320 мл</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>банка</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>KINZA цитрус — газированный безалкогольный напиток в жестяной банке 320 мл.</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Фото</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Производитель</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Вкус</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Объём</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Тара</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Описание</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Цена</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="96" customHeight="1">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Вода минеральная Kazbek-Aqua, 0,33 л, стекло</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Минеральная вода</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Kazbek-Aqua</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>0,33 л</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Минеральная вода Kazbek-Aqua в стеклянной бутылке. Рекомендуется употреблять охлаждённой.</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="96" customHeight="1">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Вода питьевая TBAU Premium газированная, 0,33 л, стекло</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>TBAU Premium</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>0,33 л</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Газированная питьевая вода TBAU в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="96" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Вода питьевая TBAU Premium газированная, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>TBAU Premium</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Газированная питьевая вода TBAU в стеклянной бутылке, объёмом 0,45 л.</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="96" customHeight="1">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Вода питьевая TBAU Premium газированная, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>TBAU Premium</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Газированная питьевая вода TBAU в стеклянной бутылке, объёмом 0,5 л.</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="96" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Вода питьевая TBAU Premium негазированная, 0,33 л, стекло</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>TBAU Premium не</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>0,33 л</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Негазированная питьевая вода TBAU в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="96" customHeight="1">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Вода питьевая TBAU Premium негазированная, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>TBAU Premium не</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Негазированная питьевая вода TBAU в стеклянной бутылке, объёмом 0,45 л.</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="96" customHeight="1">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Вода питьевая TBAU Premium негазированная, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>TBAU Premium не</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Негазированная питьевая вода TBAU в стеклянной бутылке, объёмом 0,5 л.</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="96" customHeight="1">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Вода питьевая Аварал, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Аварал</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода Аварал в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="96" customHeight="1">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Вода питьевая Айва негазированная, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Айва</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Негазированная питьевая вода Айва в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="96" customHeight="1">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Вода питьевая Горная вода газированная, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Горная вода</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Газированная питьевая вода Горная вода в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="96" customHeight="1">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Вода питьевая Горная вода негазированная, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Горная вода не</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Негазированная питьевая вода Горная вода в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="96" customHeight="1">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Cola Limited Edition газированная, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Cola Limited Edition</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Cola Limited Edition — сильногазированный безалкогольный напиток в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="96" customHeight="1">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный SWIPE газированная, 0,33 л, стекло</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>SWIPE</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>0,33 л</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>SWIPE — сильногазированный безалкогольный напиток в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="96" customHeight="1">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Premium Апельсин, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Апельсин</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Апельсин — сильногазированный безалкогольный напиток со вкусом «Апельсин» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="96" customHeight="1">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Premium Виноград, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Виноград</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Виноград — сильногазированный безалкогольный напиток со вкусом «Виноград» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="96" customHeight="1">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Premium Вишня, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Вишня</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Вишня — сильногазированный безалкогольный напиток со вкусом «Вишня» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="96" customHeight="1">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Premium Гранат, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Гранат</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Гранат — сильногазированный безалкогольный напиток со вкусом «Гранат» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="96" customHeight="1">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Premium Груша, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Груша</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Груша — сильногазированный безалкогольный напиток со вкусом «Груша» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="96" customHeight="1">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Premium Тархун, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Тархун</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Тархун — сильногазированный безалкогольный напиток со вкусом «Тархун» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="96" customHeight="1">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Premium Фейхоа, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Фейхоа</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Фейхоа — сильногазированный безалкогольный напиток со вкусом «Фейхоа» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="96" customHeight="1">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Груша, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Груша</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Груша — сильногазированный безалкогольный напиток со вкусом «Груша» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="96" customHeight="1">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Заповедная Тайга газированная, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Заповедная Тайга</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Заповедная Тайга — сильногазированный безалкогольный напиток со вкусом «Заповедная Тайга» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="96" customHeight="1">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Кола Premium LIMITED EDITION газированная, 0,33 л, стекло</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Кола Premium LIMITED EDITION</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>0,33 л</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Кола Premium LIMITED EDITION — сильногазированный безалкогольный напиток со вкусом колы в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="96" customHeight="1">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Кола Premium LIMITED EDITION газированная, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Кола Premium LIMITED EDITION</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Кола Premium LIMITED EDITION — сильногазированный безалкогольный напиток со вкусом колы в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="96" customHeight="1">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Мохито, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Мохито</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Мохито — сильногазированный безалкогольный напиток со вкусом «Мохито» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="96" customHeight="1">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Питахайя, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Питахайя</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Питахайя — сильногазированный безалкогольный напиток со вкусом «Питахайя» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="96" customHeight="1">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Родные Огоньки газированная, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Родные Огоньки</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Родные Огоньки — сильногазированный безалкогольный напиток со вкусом «Родные Огоньки» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="96" customHeight="1">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Тархун, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Тархун</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Тархун — сильногазированный безалкогольный напиток со вкусом «Тархун» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="96" customHeight="1">
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Южная Чайка газированная, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Южная Чайка</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Южная Чайка — сильногазированный безалкогольный напиток со вкусом «Южная Чайка» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="96" customHeight="1">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Пиво безалкогольное Бавария Elf, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Безалкогольное пиво</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Elf</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Elf — безалкогольное пиво в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="96" customHeight="1">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Пиво безалкогольное Бавария Gallagher, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Безалкогольное пиво</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Gallagher</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Gallagher — безалкогольное пиво в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="96" customHeight="1">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Пиво безалкогольное Бавария Светлое, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Безалкогольное пиво</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Светлое</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Светлое — безалкогольное пиво в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="n"/>
+    </row>
+    <row r="36" ht="96" customHeight="1">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Тоник Dreamix Bitter Lemon, 0,33 л, стекло</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Тоники</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Bitter Lemon</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>0,33 л</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Dreamix Bitter Lemon — безалкогольный тоник в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="96" customHeight="1">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Тоник Dreamix Indian Tonic, 0,33 л, стекло</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Тоники</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Indian Tonic</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>0,33 л</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Dreamix Indian Tonic — безалкогольный тоник в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4292,7 +6431,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Аква Дарьял, минеральная вода (0,5 л, стекло). Продукция ООО ВПБЗ «Дарьял».</t>
+          <t>Газированная минеральная вода Аква Дарьял в стеклянной бутылке. Рекомендуется употреблять охлаждённой.</t>
         </is>
       </c>
       <c r="I4" s="5" t="n"/>
@@ -4331,7 +6470,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Аква Дарьял, минеральная вода (0,5 л, стекло). Продукция ООО ВПБЗ «Дарьял».</t>
+          <t>Негазированная минеральная вода Аква Дарьял в стеклянной бутылке. Рекомендуется употреблять охлаждённой.</t>
         </is>
       </c>
       <c r="I5" s="5" t="n"/>
@@ -4370,7 +6509,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Дарьял, газированные напитки (0,5 л, стекло). Продукция ООО ВПБЗ «Дарьял».</t>
+          <t>Дарьял Апельсин-кориандр — сильногазированный безалкогольный напиток со вкусом «Апельсин-кориандр» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I6" s="5" t="n"/>
@@ -4409,7 +6548,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Дарьял, газированные напитки (0,5 л, стекло). Продукция ООО ВПБЗ «Дарьял».</t>
+          <t>Дарьял Гранат — сильногазированный безалкогольный напиток со вкусом «Гранат» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I7" s="5" t="n"/>
@@ -4448,7 +6587,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Дарьял, газированные напитки (0,5 л, стекло). Продукция ООО ВПБЗ «Дарьял».</t>
+          <t>Дарьял Груша — сильногазированный безалкогольный напиток со вкусом «Груша» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I8" s="5" t="n"/>
@@ -4487,7 +6626,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Дарьял, газированные напитки (0,5 л, стекло). Продукция ООО ВПБЗ «Дарьял».</t>
+          <t>Дарьял Кола-апельсин — сильногазированный безалкогольный напиток со вкусом колы в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I9" s="5" t="n"/>
@@ -4526,7 +6665,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Дарьял, газированные напитки (0,5 л, стекло). Продукция ООО ВПБЗ «Дарьял».</t>
+          <t>Дарьял Мохито — сильногазированный безалкогольный напиток со вкусом «Мохито» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I10" s="5" t="n"/>
@@ -4565,7 +6704,7 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>Дарьял, газированные напитки (0,5 л, стекло). Продукция ООО ВПБЗ «Дарьял».</t>
+          <t>Дарьял Тархун — сильногазированный безалкогольный напиток со вкусом «Тархун» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I11" s="5" t="n"/>
@@ -4604,7 +6743,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>Дарьял, газированные напитки (0,5 л, стекло). Продукция ООО ВПБЗ «Дарьял».</t>
+          <t>Дарьял Фейхоа-Шелковица — сильногазированный безалкогольный напиток со вкусом «Фейхоа-Шелковица» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I12" s="5" t="n"/>
@@ -4614,16 +6753,16 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4727,7 +6866,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>AquAlania, лимонады (0,5 л, стекло). Продукция AquAlania (ООО «Константа-7»).</t>
+          <t>AquAlania Барбарис — сильногазированный безалкогольный напиток со вкусом «Барбарис» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I4" s="5" t="n"/>
@@ -4766,7 +6905,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>AquAlania, лимонады (0,5 л, стекло). Продукция AquAlania (ООО «Константа-7»).</t>
+          <t>AquAlania Груша — сильногазированный безалкогольный напиток со вкусом «Груша» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I5" s="5" t="n"/>
@@ -4805,7 +6944,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>AquAlania, лимонады (0,5 л, стекло). Продукция AquAlania (ООО «Константа-7»).</t>
+          <t>AquAlania Дыня-Мята — сильногазированный безалкогольный напиток со вкусом «Дыня-Мята» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I6" s="5" t="n"/>
@@ -4844,7 +6983,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>AquAlania, кола (0,5 л, стекло). Продукция AquAlania (ООО «Константа-7»).</t>
+          <t>AquAlania Кола — сильногазированный безалкогольный напиток со вкусом колы в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I7" s="5" t="n"/>
@@ -4883,7 +7022,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>AquAlania, лимонады (0,5 л, стекло). Продукция AquAlania (ООО «Константа-7»).</t>
+          <t>AquAlania Лимонад — сильногазированный безалкогольный напиток со вкусом «Лимонад» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I8" s="5" t="n"/>
@@ -4922,7 +7061,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>AquAlania, лимонады (0,5 л, стекло). Продукция AquAlania (ООО «Константа-7»).</t>
+          <t>AquAlania Манго-Виноград — сильногазированный безалкогольный напиток со вкусом «Манго-Виноград» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I9" s="5" t="n"/>
@@ -4961,7 +7100,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>AquAlania, лимонады (0,5 л, стекло). Продукция AquAlania (ООО «Константа-7»).</t>
+          <t>AquAlania Саперави — сильногазированный безалкогольный напиток со вкусом «Саперави» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I10" s="5" t="n"/>
@@ -5000,7 +7139,7 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>AquAlania, лимонады (0,5 л, стекло). Продукция AquAlania (ООО «Константа-7»).</t>
+          <t>AquAlania Слива — сильногазированный безалкогольный напиток со вкусом «Слива» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I11" s="5" t="n"/>
@@ -5039,7 +7178,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>AquAlania, лимонады (0,5 л, стекло). Продукция AquAlania (ООО «Константа-7»).</t>
+          <t>AquAlania Тархун — сильногазированный безалкогольный напиток со вкусом «Тархун» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I12" s="5" t="n"/>
@@ -5078,7 +7217,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>AquAlania, лимонады (0,5 л, стекло). Продукция AquAlania (ООО «Константа-7»).</t>
+          <t>AquAlania Фейхоа — сильногазированный безалкогольный напиток со вкусом «Фейхоа» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I13" s="5" t="n"/>
@@ -5117,7 +7256,7 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>AquAlania, лимонады (0,5 л, стекло). Продукция AquAlania (ООО «Константа-7»).</t>
+          <t>AquAlania Игристое — сильногазированный безалкогольный напиток со вкусом «Игристое» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I14" s="5" t="n"/>
@@ -5127,16 +7266,16 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -5240,7 +7379,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>GOLD GRAND, лимонады (600 мл, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>GOLD GRAND Ананас — газированный безалкогольный напиток со вкусом «Ананас» в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I4" s="5" t="n"/>
@@ -5279,7 +7418,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>GOLD GRAND, лимонады (600 мл, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>GOLD GRAND Мохито негазированный — негазированный безалкогольный напиток со вкусом «Мохито негазированный» в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I5" s="5" t="n"/>
@@ -5318,7 +7457,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>GOLD GRAND, лимонады (600 мл, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>GOLD GRAND Мультифрукт — газированный безалкогольный напиток со вкусом «Мультифрукт» в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I6" s="5" t="n"/>
@@ -5357,7 +7496,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>GOLD GRAND, лимонады (600 мл, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>GOLD GRAND Тархун — газированный безалкогольный напиток со вкусом «Тархун» в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I7" s="5" t="n"/>
@@ -5396,7 +7535,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Ice Bar, холодный чай (500 мл, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ice Bar манго-клубника — холодный чай со вкусом «манго-клубника» в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I8" s="5" t="n"/>
@@ -5435,7 +7574,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Ice Bar, холодный чай (500 мл, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ice Bar Персик — холодный чай со вкусом «Персик» в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I9" s="5" t="n"/>
@@ -5474,7 +7613,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Ice Bar, холодный чай (500 мл, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ice Bar Ягодный — холодный чай со вкусом «Ягодный» в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I10" s="5" t="n"/>
@@ -5513,7 +7652,7 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>PROFI SPORT, энергетические напитки (500 мл, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>PROFI SPORT Energy Гуарана — безалкогольный энергетический напиток в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I11" s="5" t="n"/>
@@ -5552,7 +7691,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>Selesta, лимонады (500 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Selesta Ананас — газированный безалкогольный напиток со вкусом «Ананас» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I12" s="5" t="n"/>
@@ -5591,7 +7730,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Selesta, лимонады (500 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Selesta Гранат — газированный безалкогольный напиток со вкусом «Гранат» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I13" s="5" t="n"/>
@@ -5630,7 +7769,7 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>Selesta, лимонады (500 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Selesta Груша — газированный безалкогольный напиток со вкусом «Груша» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I14" s="5" t="n"/>
@@ -5669,7 +7808,7 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>Selesta, лимонады (500 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Selesta Мохито — газированный безалкогольный напиток со вкусом «Мохито» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I15" s="5" t="n"/>
@@ -5708,7 +7847,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Selesta, лимонады (750 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Selesta Мультифрукт — газированный безалкогольный напиток со вкусом «Мультифрукт» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I16" s="5" t="n"/>
@@ -5747,7 +7886,7 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>Selesta, лимонады (500 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Selesta Шиповник — газированный безалкогольный напиток со вкусом «Шиповник» в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I17" s="5" t="n"/>
@@ -5786,7 +7925,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Ириб, газированная вода, вкус Вода Ириб минер Тарки Тау 0 (500 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Минеральная вода Ириб в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I18" s="5" t="n"/>
@@ -5825,7 +7964,7 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>Талих, негазированная вода (1,5 л, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Питьевая вода Талих в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I19" s="5" t="n"/>
@@ -5864,7 +8003,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Талих, негазированная вода (5 л, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Питьевая вода Талих в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I20" s="5" t="n"/>
@@ -5903,7 +8042,7 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Талих, негазированная вода (600 мл, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Питьевая вода Талих в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I21" s="5" t="n"/>
@@ -5942,7 +8081,7 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Ириб, квас (1,25 л, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Янтарный — квас в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I22" s="5" t="n"/>
@@ -5981,7 +8120,7 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Ириб, нектар (3 л, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Абрикосовый — фруктовый нектар в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I23" s="5" t="n"/>
@@ -6020,7 +8159,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>Ириб, нектар (500 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Абрикосовый — фруктовый нектар в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I24" s="5" t="n"/>
@@ -6059,7 +8198,7 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Ириб, нектар (500 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Вишневый — фруктовый нектар в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I25" s="5" t="n"/>
@@ -6098,7 +8237,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>Ириб, нектар (500 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Манговый — фруктовый нектар в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I26" s="5" t="n"/>
@@ -6137,7 +8276,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Ириб, нектар (500 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Персиковый — фруктовый нектар в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I27" s="5" t="n"/>
@@ -6176,7 +8315,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>Ириб, нектар (750 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Абрикосовый — фруктовый нектар в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I28" s="5" t="n"/>
@@ -6215,7 +8354,7 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Ириб, нектар (750 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Вишневый — фруктовый нектар в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I29" s="5" t="n"/>
@@ -6254,7 +8393,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>Ириб, нектар (750 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Персиковый — фруктовый нектар в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I30" s="5" t="n"/>
@@ -6293,7 +8432,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Ириб, нектар (3 л, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Яблочно-абрикосовый — фруктовый нектар в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I31" s="5" t="n"/>
@@ -6332,7 +8471,7 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>Ириб, нектар (500 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Яблочно-абрикосовый — фруктовый нектар в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I32" s="5" t="n"/>
@@ -6371,7 +8510,7 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Ириб, нектар (3 л, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Яблочный — фруктовый нектар в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I33" s="5" t="n"/>
@@ -6410,7 +8549,7 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>Ириб, нектар (500 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Яблочный — фруктовый нектар в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I34" s="5" t="n"/>
@@ -6449,7 +8588,7 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Ириб, нектар (750 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Яблочный — фруктовый нектар в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I35" s="5" t="n"/>
@@ -6488,7 +8627,7 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>Родниковая свежесть, минеральная вода (19 л, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Минеральная вода Родниковая свежесть в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I36" s="5" t="n"/>
@@ -6527,7 +8666,7 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Родничок, питьевая вода (330 мл, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Негазированная питьевая вода Родничок в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I37" s="5" t="n"/>
@@ -6566,7 +8705,7 @@
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>Ириб, сок (500 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Ананасовый — фруктовый сок в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I38" s="5" t="n"/>
@@ -6605,7 +8744,7 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Ириб, сок (750 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Мультифруктовый — фруктовый сок в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I39" s="5" t="n"/>
@@ -6644,7 +8783,7 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>Ириб, сок (330 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Яблочный — фруктовый сок в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I40" s="5" t="n"/>
@@ -6683,7 +8822,7 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Ириб, сок (750 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Ананасовый — фруктовый сок в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I41" s="5" t="n"/>
@@ -6722,7 +8861,7 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>Ириб, сок (750 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Апельсиновый — фруктовый сок в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I42" s="5" t="n"/>
@@ -6761,7 +8900,7 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Ириб, сок (750 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб виноградный красный — фруктовый сок в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I43" s="5" t="n"/>
@@ -6800,7 +8939,7 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>Ириб, сок (750 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Гранатовый — фруктовый сок в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I44" s="5" t="n"/>
@@ -6839,7 +8978,7 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Ириб, сок (750 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Томатный — фруктовый сок в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I45" s="5" t="n"/>
@@ -6878,7 +9017,7 @@
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>Ириб, сок (750 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Яблочный — фруктовый сок в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I46" s="5" t="n"/>
@@ -6917,7 +9056,7 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Ириб, сок (3 л, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Яблочный — фруктовый сок в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I47" s="5" t="n"/>
@@ -6956,7 +9095,7 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>Ириб, сок (500 мл, стекло). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Ириб Яблочный — фруктовый сок в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I48" s="5" t="n"/>
@@ -6995,7 +9134,7 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Талих, газированные напитки (600 мл, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Талих Классический — газированный безалкогольный напиток со вкусом «Классический» в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I49" s="5" t="n"/>
@@ -7034,7 +9173,7 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>Талих, газированные напитки (600 мл, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Талих Клубника — газированный безалкогольный напиток со вкусом «Клубника» в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I50" s="5" t="n"/>
@@ -7073,7 +9212,7 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Талих, газированные напитки (600 мл, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Талих Лимон — газированный безалкогольный напиток со вкусом «Лимон» в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I51" s="5" t="n"/>
@@ -7112,7 +9251,7 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>Чегери, питьевая вода (500 мл, ПЭТ). Продукция ООО «ИРИБ» из ассортимента TINDA Маркет.</t>
+          <t>Негазированная питьевая вода Чегери в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I52" s="5" t="n"/>
@@ -7122,7 +9261,7 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -7133,7 +9272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7222,7 +9361,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7. ГК ПД «Бавария» (34)</t>
+          <t>7. Barbican (7)</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -7232,40 +9371,63 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8. ООО ВПБЗ «Дарьял» (9)</t>
+          <t>8. KINZA (7)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9. ООО «Константа-7» (11)</t>
+          <t>9. ГК ПД «Бавария» (34)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10. ООО «ИРИБ» (49)</t>
+          <t>10. ООО ВПБЗ «Дарьял» (9)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>11. ООО «Константа-7» (11)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12. ООО «ИРИБ» (49)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>22</v>
+      </c>
+    </row>
     <row r="16"/>
     <row r="17"/>
     <row r="18"/>
     <row r="19"/>
     <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7275,7 +9437,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -7379,7 +9541,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Coca-Cola, кола (0,33 л, жестяная банка) — классический сильногазированный безалкогольный напиток. Подходит для употребления в охлаждённом виде.</t>
+          <t>Coca-Cola Original Taste — классический сильногазированный безалкогольный напиток с насыщенным вкусом в жестяной банке. Подходит для употребления в охлаждённом виде.</t>
         </is>
       </c>
       <c r="I4" s="5" t="n"/>
@@ -7418,7 +9580,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Coca-Cola, кола (0,33 л, стекло) — классический сильногазированный безалкогольный напиток. Подходит для употребления в охлаждённом виде.</t>
+          <t>Coca-Cola Original Taste — классический сильногазированный безалкогольный напиток с насыщенным вкусом в стеклянной бутылке. Подходит для употребления в охлаждённом виде.</t>
         </is>
       </c>
       <c r="I5" s="5" t="n"/>
@@ -7457,7 +9619,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Coca-Cola, кола (0,33 л, жестяная банка) — классический сильногазированный безалкогольный напиток. Подходит для употребления в охлаждённом виде.</t>
+          <t>Coca-Cola Zero без кофеина — безалкогольный сильногазированный напиток без сахара и без кофеина в жестяной банке. Подходит для употребления в охлаждённом виде.</t>
         </is>
       </c>
       <c r="I6" s="5" t="n"/>
@@ -7496,7 +9658,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Coca-Cola, кола (0,33 л, жестяная банка) — классический сильногазированный безалкогольный напиток. Подходит для употребления в охлаждённом виде.</t>
+          <t>Coca-Cola Zero — безалкогольный сильногазированный напиток без сахара в жестяной банке. Подходит для употребления в охлаждённом виде.</t>
         </is>
       </c>
       <c r="I7" s="5" t="n"/>
@@ -7535,7 +9697,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Coca-Cola, кола (0,33 л, стекло) — классический сильногазированный безалкогольный напиток. Подходит для употребления в охлаждённом виде.</t>
+          <t>Coca-Cola Zero — безалкогольный сильногазированный напиток без сахара в стеклянной бутылке. Подходит для употребления в охлаждённом виде.</t>
         </is>
       </c>
       <c r="I8" s="5" t="n"/>
@@ -7545,7 +9707,7 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -7554,7 +9716,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -7658,7 +9820,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Sprite, лимонады, вкус лимон и лайм (0,33 л, жестяная банка) — классический сильногазированный безалкогольный напиток. Подходит для употребления в охлаждённом виде.</t>
+          <t>Sprite — сильногазированный безалкогольный напиток со вкусом лимона и лайма в жестяной банке.</t>
         </is>
       </c>
       <c r="I4" s="5" t="n"/>
@@ -7697,7 +9859,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Sprite, газированные напитки, вкус лимон и лайм (2 л, ПЭТ) — классический сильногазированный безалкогольный напиток. Подходит для употребления в охлаждённом виде.</t>
+          <t>Sprite — сильногазированный безалкогольный напиток со вкусом лимона и лайма в ПЭТ-бутылке.</t>
         </is>
       </c>
       <c r="I5" s="5" t="n"/>
@@ -7707,7 +9869,7 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -7716,7 +9878,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -7816,7 +9978,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Боржоми, газированная вода (330 мл, стекло). Минеральная / питьевая вода из ассортимента TINDA Маркет.</t>
+          <t>Минеральная вода Borjomi природной минерализации в стеклянной бутылке. Рекомендуется употреблять охлаждённой.</t>
         </is>
       </c>
       <c r="I4" s="5" t="n"/>
@@ -7851,7 +10013,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Боржоми, газированная вода (500 мл, стекло). Минеральная / питьевая вода из ассортимента TINDA Маркет.</t>
+          <t>Минеральная вода Borjomi природной минерализации в стеклянной бутылке. Рекомендуется употреблять охлаждённой, объёмом 500 мл.</t>
         </is>
       </c>
       <c r="I5" s="5" t="n"/>
@@ -7861,7 +10023,7 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -7870,7 +10032,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -7970,7 +10132,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>мин, газированная вода (500 мл, стекло). Минеральная / питьевая вода из ассортимента TINDA Маркет.</t>
+          <t>Минеральная вода Рычал-Су в стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I4" s="5" t="n"/>
@@ -7980,7 +10142,7 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -7989,7 +10151,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -8093,7 +10255,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Adrenaline Rush, энергетические напитки (0,25 л, жестяная банка). Энергетический напиток для бодрящего эффекта.</t>
+          <t>Adrenaline Rush — безалкогольный энергетический напиток.</t>
         </is>
       </c>
       <c r="I4" s="5" t="n"/>
@@ -8132,7 +10294,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Adrenaline Rush, энергетические напитки (0,449 л, жестяная банка). Энергетический напиток для бодрящего эффекта.</t>
+          <t>Adrenaline Rush — безалкогольный энергетический напиток.</t>
         </is>
       </c>
       <c r="I5" s="5" t="n"/>
@@ -8142,7 +10304,7 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -8151,7 +10313,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -8255,7 +10417,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Вико, нектар (1 л, картон). Соковая продукция Viko из ассортимента TINDA Маркет.</t>
+          <t>Вико Абрикос — фруктовый нектар объёмом 1 литр.</t>
         </is>
       </c>
       <c r="I4" s="5" t="n"/>
@@ -8294,7 +10456,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Вико, нектар (1 л, картон). Соковая продукция Viko из ассортимента TINDA Маркет.</t>
+          <t>Вико Банан — фруктовый нектар объёмом 1 литр.</t>
         </is>
       </c>
       <c r="I5" s="5" t="n"/>
@@ -8333,7 +10495,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Вико, сок (1 л, картон). Соковая продукция Viko из ассортимента TINDA Маркет.</t>
+          <t>Вико Ананас — восстановленный фруктовый сок объёмом 1 литр.</t>
         </is>
       </c>
       <c r="I6" s="5" t="n"/>
@@ -8372,7 +10534,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Вико, сок, вкус Апельсин-манго (1 л, картон). Соковая продукция Viko из ассортимента TINDA Маркет.</t>
+          <t>Вико Апельсин-манго — восстановленный фруктовый сок объёмом 1 литр.</t>
         </is>
       </c>
       <c r="I7" s="5" t="n"/>
@@ -8411,7 +10573,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Вико, сок (1 л, картон). Соковая продукция Viko из ассортимента TINDA Маркет.</t>
+          <t>Вико Апельсин — восстановленный фруктовый сок объёмом 1 литр.</t>
         </is>
       </c>
       <c r="I8" s="5" t="n"/>
@@ -8450,7 +10612,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Вико, сок, вкус Виноград-яблоко (1 л, картон). Соковая продукция Viko из ассортимента TINDA Маркет.</t>
+          <t>Вико Виноград-яблоко — восстановленный фруктовый сок объёмом 1 литр.</t>
         </is>
       </c>
       <c r="I9" s="5" t="n"/>
@@ -8489,7 +10651,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Вико, сок, вкус Чёрный виноград (1 л, картон). Соковая продукция Viko из ассортимента TINDA Маркет.</t>
+          <t>Вико Чёрный виноград — восстановленный фруктовый сок объёмом 1 литр.</t>
         </is>
       </c>
       <c r="I10" s="5" t="n"/>
@@ -8528,7 +10690,7 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>Вико, сок, вкус Вишня (1 л, картон). Соковая продукция Viko из ассортимента TINDA Маркет.</t>
+          <t>Вико Вишня — восстановленный фруктовый сок объёмом 1 литр.</t>
         </is>
       </c>
       <c r="I11" s="5" t="n"/>
@@ -8567,7 +10729,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>Вико, сок (1 л, картон). Соковая продукция Viko из ассортимента TINDA Маркет.</t>
+          <t>Вико Гранат — восстановленный фруктовый сок объёмом 1 литр.</t>
         </is>
       </c>
       <c r="I12" s="5" t="n"/>
@@ -8606,7 +10768,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Вико, сок, вкус Зелёное яблоко (1 л, картон). Соковая продукция Viko из ассортимента TINDA Маркет.</t>
+          <t>Вико Зелёное яблоко — восстановленный фруктовый сок объёмом 1 литр.</t>
         </is>
       </c>
       <c r="I13" s="5" t="n"/>
@@ -8645,7 +10807,7 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>Вико, сок (1 л, картон). Соковая продукция Viko из ассортимента TINDA Маркет.</t>
+          <t>Вико Мультифрукт — восстановленный фруктовый сок объёмом 1 литр.</t>
         </is>
       </c>
       <c r="I14" s="5" t="n"/>
@@ -8684,7 +10846,7 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>Вико, сок (1 л, картон). Соковая продукция Viko из ассортимента TINDA Маркет.</t>
+          <t>Вико Персик — восстановленный фруктовый сок объёмом 1 литр.</t>
         </is>
       </c>
       <c r="I15" s="5" t="n"/>
@@ -8723,7 +10885,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Вико, сок (1 л, картон). Соковая продукция Viko из ассортимента TINDA Маркет.</t>
+          <t>Вико Томат — восстановленный фруктовый сок объёмом 1 литр.</t>
         </is>
       </c>
       <c r="I16" s="5" t="n"/>
@@ -8733,7 +10895,7 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -8742,9 +10904,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8761,7 +10923,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>ГК ПД «Бавария»</t>
+          <t>Barbican</t>
         </is>
       </c>
     </row>
@@ -8816,27 +10978,27 @@
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Вода минеральная Kazbek-Aqua, 0,33 л, стекло</t>
+          <t>Напиток Barbican Malt ячмень ст 330мл</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ГК ПД «Бавария»</t>
+          <t>Barbican</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Минеральная вода</t>
+          <t>Безалкогольное пиво</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Kazbek-Aqua</t>
+          <t>Malt / ячмень</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>0,33 л</t>
+          <t>330 мл</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -8846,7 +11008,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Kazbek-Aqua, минеральная вода (0,33 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
+          <t>Barbican Malt / ячмень — безалкогольный солодовый напиток в стеклянной бутылке 330 мл.</t>
         </is>
       </c>
       <c r="I4" s="5" t="n"/>
@@ -8855,27 +11017,27 @@
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Вода питьевая TBAU Premium газированная, 0,33 л, стекло</t>
+          <t>Напиток Barbican ананас ст 330мл</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>ГК ПД «Бавария»</t>
+          <t>Barbican</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Питьевая вода</t>
+          <t>Безалкогольное пиво</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>TBAU Premium</t>
+          <t>ананас</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>0,33 л</t>
+          <t>330 мл</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -8885,7 +11047,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>TBAU, питьевая вода (0,33 л, стекло). Минеральная / питьевая вода из ассортимента TINDA Маркет.</t>
+          <t>Barbican ананас — безалкогольный солодовый напиток в стеклянной бутылке 330 мл.</t>
         </is>
       </c>
       <c r="I5" s="5" t="n"/>
@@ -8894,27 +11056,27 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Вода питьевая TBAU Premium газированная, 0,45 л, стекло</t>
+          <t>Напиток Barbican гранат ст 330мл</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>ГК ПД «Бавария»</t>
+          <t>Barbican</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Питьевая вода</t>
+          <t>Безалкогольное пиво</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>TBAU Premium</t>
+          <t>гранат</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>0,45 л</t>
+          <t>330 мл</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -8924,7 +11086,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>TBAU, питьевая вода (0,45 л, стекло). Минеральная / питьевая вода из ассортимента TINDA Маркет.</t>
+          <t>Barbican гранат — безалкогольный солодовый напиток в стеклянной бутылке 330 мл.</t>
         </is>
       </c>
       <c r="I6" s="5" t="n"/>
@@ -8933,27 +11095,27 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Вода питьевая TBAU Premium газированная, 0,5 л, стекло</t>
+          <t>Напиток Barbican лимон ст 330мл</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>ГК ПД «Бавария»</t>
+          <t>Barbican</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Питьевая вода</t>
+          <t>Безалкогольное пиво</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>TBAU Premium</t>
+          <t>лимон</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0,5 л</t>
+          <t>330 мл</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -8963,7 +11125,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>TBAU, питьевая вода (0,5 л, стекло). Минеральная / питьевая вода из ассортимента TINDA Маркет.</t>
+          <t>Barbican лимон — безалкогольный солодовый напиток в стеклянной бутылке 330 мл.</t>
         </is>
       </c>
       <c r="I7" s="5" t="n"/>
@@ -8972,27 +11134,27 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Вода питьевая TBAU Premium негазированная, 0,33 л, стекло</t>
+          <t>Напиток Barbican малина ст 330мл</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>ГК ПД «Бавария»</t>
+          <t>Barbican</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Питьевая вода</t>
+          <t>Безалкогольное пиво</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>TBAU Premium не</t>
+          <t>малина</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>0,33 л</t>
+          <t>330 мл</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -9002,7 +11164,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>TBAU, питьевая вода (0,33 л, стекло). Минеральная / питьевая вода из ассортимента TINDA Маркет.</t>
+          <t>Barbican малина — безалкогольный солодовый напиток в стеклянной бутылке 330 мл.</t>
         </is>
       </c>
       <c r="I8" s="5" t="n"/>
@@ -9011,27 +11173,27 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Вода питьевая TBAU Premium негазированная, 0,45 л, стекло</t>
+          <t>Напиток Barbican персик ст 330мл</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>ГК ПД «Бавария»</t>
+          <t>Barbican</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Питьевая вода</t>
+          <t>Безалкогольное пиво</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>TBAU Premium не</t>
+          <t>персик</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0,45 л</t>
+          <t>330 мл</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -9041,7 +11203,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>TBAU, питьевая вода (0,45 л, стекло). Минеральная / питьевая вода из ассортимента TINDA Маркет.</t>
+          <t>Barbican персик — безалкогольный солодовый напиток в стеклянной бутылке 330 мл.</t>
         </is>
       </c>
       <c r="I9" s="5" t="n"/>
@@ -9050,27 +11212,27 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Вода питьевая TBAU Premium негазированная, 0,5 л, стекло</t>
+          <t>Напиток Barbican яблоко ст 330мл</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>ГК ПД «Бавария»</t>
+          <t>Barbican</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Питьевая вода</t>
+          <t>Безалкогольное пиво</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>TBAU Premium не</t>
+          <t>яблоко</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>0,5 л</t>
+          <t>330 мл</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -9080,1070 +11242,17 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>TBAU, питьевая вода (0,5 л, стекло). Минеральная / питьевая вода из ассортимента TINDA Маркет.</t>
+          <t>Barbican яблоко — безалкогольный солодовый напиток в стеклянной бутылке 330 мл.</t>
         </is>
       </c>
       <c r="I10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="96" customHeight="1">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Вода питьевая Аварал, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Питьевая вода</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Аварал</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Аварал, питьевая вода (0,45 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="96" customHeight="1">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Вода питьевая Айва негазированная, 0,5 л, стекло</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Питьевая вода</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Айва</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>0,5 л</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>Айва, питьевая вода (0,5 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="96" customHeight="1">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Вода питьевая Горная вода газированная, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Питьевая вода</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Горная вода</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>Горная вода, питьевая вода (0,45 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="96" customHeight="1">
-      <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Вода питьевая Горная вода негазированная, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Питьевая вода</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Горная вода не</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>Горная вода, питьевая вода (0,45 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="96" customHeight="1">
-      <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Cola Limited Edition газированная, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Cola Limited Edition</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>Cola Limited Edition, газированные напитки (0,45 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="96" customHeight="1">
-      <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный SWIPE газированная, 0,33 л, стекло</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>SWIPE</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>0,33 л</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>SWIPE, газированные напитки (0,33 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="96" customHeight="1">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Premium Апельсин, 0,5 л, стекло</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Апельсин</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>0,5 л</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>Бавария, газированные напитки (0,5 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="96" customHeight="1">
-      <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Premium Виноград, 0,5 л, стекло</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Виноград</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>0,5 л</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>Бавария, газированные напитки (0,5 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="96" customHeight="1">
-      <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Premium Вишня, 0,5 л, стекло</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Вишня</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>0,5 л</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>Бавария, газированные напитки (0,5 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="96" customHeight="1">
-      <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Premium Гранат, 0,5 л, стекло</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Гранат</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>0,5 л</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>Бавария, газированные напитки (0,5 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="96" customHeight="1">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Premium Груша, 0,5 л, стекло</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Груша</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>0,5 л</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Бавария, газированные напитки (0,5 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="96" customHeight="1">
-      <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Premium Тархун, 0,5 л, стекло</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Тархун</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>0,5 л</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>Бавария, газированные напитки (0,5 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="96" customHeight="1">
-      <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Premium Фейхоа, 0,5 л, стекло</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Фейхоа</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>0,5 л</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Бавария, газированные напитки (0,5 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="96" customHeight="1">
-      <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Груша, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Груша</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>Бавария, газированные напитки (0,45 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="96" customHeight="1">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Заповедная Тайга газированная, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Заповедная Тайга</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Бавария, газированные напитки (0,45 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="96" customHeight="1">
-      <c r="A26" s="5" t="n"/>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Кола Premium LIMITED EDITION газированная, 0,33 л, стекло</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Кола Premium LIMITED EDITION</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>0,33 л</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>Бавария, газированные напитки (0,33 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="96" customHeight="1">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Кола Premium LIMITED EDITION газированная, 0,5 л, стекло</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Кола Premium LIMITED EDITION</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>0,5 л</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Бавария, газированные напитки (0,5 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="96" customHeight="1">
-      <c r="A28" s="5" t="n"/>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Мохито, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Мохито</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>Бавария, газированные напитки (0,45 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="96" customHeight="1">
-      <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Питахайя, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Питахайя</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Бавария, газированные напитки (0,45 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="96" customHeight="1">
-      <c r="A30" s="5" t="n"/>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Родные Огоньки газированная, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Родные Огоньки</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>Бавария, газированные напитки (0,45 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="96" customHeight="1">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Тархун, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Тархун</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Бавария, газированные напитки (0,45 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="n"/>
-    </row>
-    <row r="32" ht="96" customHeight="1">
-      <c r="A32" s="5" t="n"/>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Южная Чайка газированная, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>Южная Чайка</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>Бавария, газированные напитки (0,45 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="n"/>
-    </row>
-    <row r="33" ht="96" customHeight="1">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Пиво безалкогольное Бавария Elf, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Безалкогольное пиво</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Elf</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Бавария, безалкогольное пиво (0,45 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="n"/>
-    </row>
-    <row r="34" ht="96" customHeight="1">
-      <c r="A34" s="5" t="n"/>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Пиво безалкогольное Бавария Gallagher, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>Безалкогольное пиво</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>Gallagher</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>Бавария, безалкогольное пиво (0,45 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="n"/>
-    </row>
-    <row r="35" ht="96" customHeight="1">
-      <c r="A35" s="5" t="n"/>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Пиво безалкогольное Бавария Светлое, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Безалкогольное пиво</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>Светлое</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>Бавария, безалкогольное пиво (0,45 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="n"/>
-    </row>
-    <row r="36" ht="96" customHeight="1">
-      <c r="A36" s="5" t="n"/>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Тоник Dreamix Bitter Lemon, 0,33 л, стекло</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Тоники</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>Bitter Lemon</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>0,33 л</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>Dreamix, тоники (0,33 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="n"/>
-    </row>
-    <row r="37" ht="96" customHeight="1">
-      <c r="A37" s="5" t="n"/>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Тоник Dreamix Indian Tonic, 0,33 л, стекло</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Тоники</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>Indian Tonic</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>0,33 л</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>Dreamix, тоники (0,33 л, стекло). Газированный напиток производства ГК ПД «Бавария».</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/artifacts/commercial-price-list-2026-08-05/TINDA-Каталог продукции.xlsx
+++ b/artifacts/commercial-price-list-2026-08-05/TINDA-Каталог продукции.xlsx
@@ -17,10 +17,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Viko" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Barbican" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KINZA" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ГК ПД «Бавария»" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ООО ВПБЗ «Дарьял»" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ООО «Константа-7»" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ООО «ИРИБ»" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="От винта!" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Зеленокумский" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нальчикский" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ГК ПД «Бавария»" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ООО ВПБЗ «Дарьял»" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ООО «Константа-7»" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ООО «ИРИБ»" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,706 +470,6 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>12</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>13</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="12" name="Image 12" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>15</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="13" name="Image 13" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>20</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="20" name="Image 20" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>23</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="21" name="Image 21" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>24</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="22" name="Image 22" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>25</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="23" name="Image 23" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>26</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="24" name="Image 24" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="25" name="Image 25" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>28</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="26" name="Image 26" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>29</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="27" name="Image 27" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>30</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>31</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="30" name="Image 30" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>33</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="31" name="Image 31" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>34</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="32" name="Image 32" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="33" name="Image 33" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="34" name="Image 34" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1368,62 +671,6 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1741,6 +988,1533 @@
 </file>
 
 <file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -4571,11 +5345,11 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -4923,16 +5697,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -4940,7 +5714,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>ГК ПД «Бавария»</t>
+          <t>От винта!</t>
         </is>
       </c>
     </row>
@@ -4995,27 +5769,27 @@
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Вода минеральная Kazbek-Aqua, 0,33 л, стекло</t>
+          <t>От винта! Барбарис, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ГК ПД «Бавария»</t>
+          <t>От винта! (Продако)</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Минеральная вода</t>
+          <t>Лимонады</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Kazbek-Aqua</t>
+          <t>Барбарис</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>0,33 л</t>
+          <t>0,5 л</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -5025,7 +5799,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Минеральная вода Kazbek-Aqua в стеклянной бутылке. Рекомендуется употреблять охлаждённой.</t>
+          <t>Сильногазированный лимонад «От винта!» со вкусом барбариса. Готовится по технологии варки сахарного сиропа 1970 года; зелёная стеклянная бутылка защищает вкус от света.</t>
         </is>
       </c>
       <c r="I4" s="5" t="n"/>
@@ -5034,27 +5808,27 @@
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Вода питьевая TBAU Premium газированная, 0,33 л, стекло</t>
+          <t>От винта! Груша, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>ГК ПД «Бавария»</t>
+          <t>От винта! (Продако)</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Питьевая вода</t>
+          <t>Лимонады</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>TBAU Premium</t>
+          <t>Груша</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>0,33 л</t>
+          <t>0,5 л</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -5064,7 +5838,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Газированная питьевая вода TBAU в стеклянной бутылке.</t>
+          <t>Сильногазированный лимонад «От винта!» со вкусом груши. Бренд Продако, классическая стеклянная тара.</t>
         </is>
       </c>
       <c r="I5" s="5" t="n"/>
@@ -5073,27 +5847,27 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Вода питьевая TBAU Premium газированная, 0,45 л, стекло</t>
+          <t>От винта! Золотой ключик, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>ГК ПД «Бавария»</t>
+          <t>От винта! (Продако)</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Питьевая вода</t>
+          <t>Лимонады</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>TBAU Premium</t>
+          <t>Золотой ключик</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>0,45 л</t>
+          <t>0,5 л</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -5103,7 +5877,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Газированная питьевая вода TBAU в стеклянной бутылке, объёмом 0,45 л.</t>
+          <t>Сильногазированный лимонад «От винта!» со вкусом «Золотой ключик» по рецептуре варки сиропа 1970 года.</t>
         </is>
       </c>
       <c r="I6" s="5" t="n"/>
@@ -5112,22 +5886,22 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Вода питьевая TBAU Premium газированная, 0,5 л, стекло</t>
+          <t>От винта! Кола, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>ГК ПД «Бавария»</t>
+          <t>От винта! (Продако)</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Питьевая вода</t>
+          <t>Лимонады</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>TBAU Premium</t>
+          <t>Кола</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -5142,7 +5916,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Газированная питьевая вода TBAU в стеклянной бутылке, объёмом 0,5 л.</t>
+          <t>Сильногазированный напиток «От винта!» со вкусом колы в ассортименте бренда Продако.</t>
         </is>
       </c>
       <c r="I7" s="5" t="n"/>
@@ -5151,27 +5925,27 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Вода питьевая TBAU Premium негазированная, 0,33 л, стекло</t>
+          <t>От винта! Лимонад, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>ГК ПД «Бавария»</t>
+          <t>От винта! (Продако)</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Питьевая вода</t>
+          <t>Лимонады</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>TBAU Premium не</t>
+          <t>Лимонад</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>0,33 л</t>
+          <t>0,5 л</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -5181,7 +5955,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Негазированная питьевая вода TBAU в стеклянной бутылке.</t>
+          <t>Классический сильногазированный лимонад «От винта!» в зелёной стеклянной бутылке — вкус советского лимонада.</t>
         </is>
       </c>
       <c r="I8" s="5" t="n"/>
@@ -5190,27 +5964,27 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Вода питьевая TBAU Premium негазированная, 0,45 л, стекло</t>
+          <t>От винта! Мохито клубника, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>ГК ПД «Бавария»</t>
+          <t>От винта! (Продако)</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Питьевая вода</t>
+          <t>Лимонады</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>TBAU Premium не</t>
+          <t>Мохито клубника</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0,45 л</t>
+          <t>0,5 л</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -5220,7 +5994,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Негазированная питьевая вода TBAU в стеклянной бутылке, объёмом 0,45 л.</t>
+          <t>Сильногазированный напиток «От винта!» со вкусом клубничного мохито в зелёной стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I9" s="5" t="n"/>
@@ -5229,22 +6003,22 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Вода питьевая TBAU Premium негазированная, 0,5 л, стекло</t>
+          <t>От винта! Мохито, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>ГК ПД «Бавария»</t>
+          <t>От винта! (Продако)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Питьевая вода</t>
+          <t>Лимонады</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>TBAU Premium не</t>
+          <t>Мохито</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -5259,7 +6033,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Негазированная питьевая вода TBAU в стеклянной бутылке, объёмом 0,5 л.</t>
+          <t>Сильногазированный лимонад «От винта!» со вкусом мохито (лайм и мята). Технология варки сиропа 1970 года.</t>
         </is>
       </c>
       <c r="I10" s="5" t="n"/>
@@ -5268,27 +6042,27 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Вода питьевая Аварал, 0,45 л, стекло</t>
+          <t>От винта! Тархун, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>ГК ПД «Бавария»</t>
+          <t>От винта! (Продако)</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Питьевая вода</t>
+          <t>Лимонады</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Аварал</t>
+          <t>Тархун</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>0,45 л</t>
+          <t>0,5 л</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -5298,7 +6072,7 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>Питьевая вода Аварал в стеклянной бутылке.</t>
+          <t>Сильногазированный напиток «От винта!» со вкусом тархуна (эстрагона) в фирменной зелёной стеклянной бутылке.</t>
         </is>
       </c>
       <c r="I11" s="5" t="n"/>
@@ -5307,22 +6081,22 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Вода питьевая Айва негазированная, 0,5 л, стекло</t>
+          <t>От винта! Таёжник, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>ГК ПД «Бавария»</t>
+          <t>От винта! (Продако)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Питьевая вода</t>
+          <t>Лимонады</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Айва</t>
+          <t>Таёжник</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -5337,985 +6111,10 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>Негазированная питьевая вода Айва в стеклянной бутылке.</t>
+          <t>Сильногазированный напиток «От винта!» со вкусом «Таёжник» — один из традиционных вкусов линейки.</t>
         </is>
       </c>
       <c r="I12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="96" customHeight="1">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Вода питьевая Горная вода газированная, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Питьевая вода</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Горная вода</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>Газированная питьевая вода Горная вода в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="96" customHeight="1">
-      <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Вода питьевая Горная вода негазированная, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Питьевая вода</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Горная вода не</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>Негазированная питьевая вода Горная вода в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="96" customHeight="1">
-      <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Cola Limited Edition газированная, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Cola Limited Edition</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>Cola Limited Edition — сильногазированный безалкогольный напиток в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="96" customHeight="1">
-      <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный SWIPE газированная, 0,33 л, стекло</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>SWIPE</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>0,33 л</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>SWIPE — сильногазированный безалкогольный напиток в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="96" customHeight="1">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Premium Апельсин, 0,5 л, стекло</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Апельсин</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>0,5 л</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>Бавария Апельсин — сильногазированный безалкогольный напиток со вкусом «Апельсин» в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="96" customHeight="1">
-      <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Premium Виноград, 0,5 л, стекло</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Виноград</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>0,5 л</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>Бавария Виноград — сильногазированный безалкогольный напиток со вкусом «Виноград» в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="96" customHeight="1">
-      <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Premium Вишня, 0,5 л, стекло</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Вишня</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>0,5 л</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>Бавария Вишня — сильногазированный безалкогольный напиток со вкусом «Вишня» в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="96" customHeight="1">
-      <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Premium Гранат, 0,5 л, стекло</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Гранат</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>0,5 л</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>Бавария Гранат — сильногазированный безалкогольный напиток со вкусом «Гранат» в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="96" customHeight="1">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Premium Груша, 0,5 л, стекло</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Груша</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>0,5 л</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Бавария Груша — сильногазированный безалкогольный напиток со вкусом «Груша» в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="96" customHeight="1">
-      <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Premium Тархун, 0,5 л, стекло</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Тархун</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>0,5 л</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>Бавария Тархун — сильногазированный безалкогольный напиток со вкусом «Тархун» в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="96" customHeight="1">
-      <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Premium Фейхоа, 0,5 л, стекло</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Фейхоа</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>0,5 л</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Бавария Фейхоа — сильногазированный безалкогольный напиток со вкусом «Фейхоа» в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="96" customHeight="1">
-      <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Груша, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Груша</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>Бавария Груша — сильногазированный безалкогольный напиток со вкусом «Груша» в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="96" customHeight="1">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Заповедная Тайга газированная, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Заповедная Тайга</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Бавария Заповедная Тайга — сильногазированный безалкогольный напиток со вкусом «Заповедная Тайга» в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="96" customHeight="1">
-      <c r="A26" s="5" t="n"/>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Кола Premium LIMITED EDITION газированная, 0,33 л, стекло</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Кола Premium LIMITED EDITION</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>0,33 л</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>Бавария Кола Premium LIMITED EDITION — сильногазированный безалкогольный напиток со вкусом колы в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="96" customHeight="1">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Кола Premium LIMITED EDITION газированная, 0,5 л, стекло</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Кола Premium LIMITED EDITION</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>0,5 л</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Бавария Кола Premium LIMITED EDITION — сильногазированный безалкогольный напиток со вкусом колы в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="96" customHeight="1">
-      <c r="A28" s="5" t="n"/>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Мохито, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Мохито</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>Бавария Мохито — сильногазированный безалкогольный напиток со вкусом «Мохито» в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="96" customHeight="1">
-      <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Питахайя, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Питахайя</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Бавария Питахайя — сильногазированный безалкогольный напиток со вкусом «Питахайя» в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="96" customHeight="1">
-      <c r="A30" s="5" t="n"/>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Родные Огоньки газированная, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Родные Огоньки</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>Бавария Родные Огоньки — сильногазированный безалкогольный напиток со вкусом «Родные Огоньки» в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="96" customHeight="1">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Тархун, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Тархун</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Бавария Тархун — сильногазированный безалкогольный напиток со вкусом «Тархун» в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="n"/>
-    </row>
-    <row r="32" ht="96" customHeight="1">
-      <c r="A32" s="5" t="n"/>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Напиток газированный Бавария Южная Чайка газированная, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>Южная Чайка</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>Бавария Южная Чайка — сильногазированный безалкогольный напиток со вкусом «Южная Чайка» в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="n"/>
-    </row>
-    <row r="33" ht="96" customHeight="1">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Пиво безалкогольное Бавария Elf, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Безалкогольное пиво</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Elf</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Бавария Elf — безалкогольное пиво в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="n"/>
-    </row>
-    <row r="34" ht="96" customHeight="1">
-      <c r="A34" s="5" t="n"/>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Пиво безалкогольное Бавария Gallagher, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>Безалкогольное пиво</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>Gallagher</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>Бавария Gallagher — безалкогольное пиво в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="n"/>
-    </row>
-    <row r="35" ht="96" customHeight="1">
-      <c r="A35" s="5" t="n"/>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Пиво безалкогольное Бавария Светлое, 0,45 л, стекло</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Безалкогольное пиво</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>Светлое</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>0,45 л</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>Бавария Светлое — безалкогольное пиво в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="n"/>
-    </row>
-    <row r="36" ht="96" customHeight="1">
-      <c r="A36" s="5" t="n"/>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Тоник Dreamix Bitter Lemon, 0,33 л, стекло</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Тоники</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>Bitter Lemon</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>0,33 л</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>Dreamix Bitter Lemon — безалкогольный тоник в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="n"/>
-    </row>
-    <row r="37" ht="96" customHeight="1">
-      <c r="A37" s="5" t="n"/>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Тоник Dreamix Indian Tonic, 0,33 л, стекло</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>ГК ПД «Бавария»</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Тоники</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>Indian Tonic</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>0,33 л</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>Dreamix Indian Tonic — безалкогольный тоник в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6333,16 +6132,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -6350,7 +6149,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>ООО ВПБЗ «Дарьял»</t>
+          <t>Зеленокумский</t>
         </is>
       </c>
     </row>
@@ -6405,20 +6204,24 @@
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Аква Дарьял газированная, 0,5 л, стекло</t>
+          <t>Зеленокумский Барбарис, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ООО ВПБЗ «Дарьял»</t>
+          <t>АО «Зеленокумский пивоваренный завод»</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Минеральная вода</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr"/>
+          <t>Лимонады</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Барбарис</t>
+        </is>
+      </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
           <t>0,5 л</t>
@@ -6431,7 +6234,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Газированная минеральная вода Аква Дарьял в стеклянной бутылке. Рекомендуется употреблять охлаждённой.</t>
+          <t>Газированный лимонад Зеленокумский со вкусом барбариса. Классическая стеклянная бутылка 0,5 л.</t>
         </is>
       </c>
       <c r="I4" s="5" t="n"/>
@@ -6440,22 +6243,22 @@
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Аква Дарьял негазированная, 0,5 л, стекло</t>
+          <t>Зеленокумский Груша, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>ООО ВПБЗ «Дарьял»</t>
+          <t>АО «Зеленокумский пивоваренный завод»</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Минеральная вода</t>
+          <t>Лимонады</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>не</t>
+          <t>Груша</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -6470,7 +6273,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Негазированная минеральная вода Аква Дарьял в стеклянной бутылке. Рекомендуется употреблять охлаждённой.</t>
+          <t>Газированный лимонад Зеленокумский со вкусом груши. Производство АО «Зеленокумский пивоваренный завод» (Ставропольский край).</t>
         </is>
       </c>
       <c r="I5" s="5" t="n"/>
@@ -6479,22 +6282,22 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Дарьял Апельсин-кориандр газированная, 0,5 л, стекло</t>
+          <t>Зеленокумский Лимон, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>ООО ВПБЗ «Дарьял»</t>
+          <t>АО «Зеленокумский пивоваренный завод»</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Газированные напитки</t>
+          <t>Лимонады</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Апельсин-кориандр</t>
+          <t>Лимон</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -6509,7 +6312,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Дарьял Апельсин-кориандр — сильногазированный безалкогольный напиток со вкусом «Апельсин-кориандр» в стеклянной бутылке.</t>
+          <t>Газированный лимонад Зеленокумский со вкусом лимона в стеклянной бутылке 0,5 л.</t>
         </is>
       </c>
       <c r="I6" s="5" t="n"/>
@@ -6518,22 +6321,22 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Дарьял Гранат газированная, 0,5 л, стекло</t>
+          <t>Зеленокумский Лимонад, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>ООО ВПБЗ «Дарьял»</t>
+          <t>АО «Зеленокумский пивоваренный завод»</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Газированные напитки</t>
+          <t>Лимонады</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Гранат</t>
+          <t>Лимонад</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -6548,7 +6351,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Дарьял Гранат — сильногазированный безалкогольный напиток со вкусом «Гранат» в стеклянной бутылке.</t>
+          <t>Классический газированный лимонад Зеленокумский в стеклянной бутылке 0,5 л.</t>
         </is>
       </c>
       <c r="I7" s="5" t="n"/>
@@ -6557,22 +6360,22 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Дарьял Груша газированная, 0,5 л, стекло</t>
+          <t>Зеленокумский Мохито, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>ООО ВПБЗ «Дарьял»</t>
+          <t>АО «Зеленокумский пивоваренный завод»</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Газированные напитки</t>
+          <t>Лимонады</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Груша</t>
+          <t>Мохито</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -6587,7 +6390,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Дарьял Груша — сильногазированный безалкогольный напиток со вкусом «Груша» в стеклянной бутылке.</t>
+          <t>Газированный лимонад Зеленокумский со вкусом мохито. Производство Зеленокумского пивоваренного завода.</t>
         </is>
       </c>
       <c r="I8" s="5" t="n"/>
@@ -6596,22 +6399,22 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Дарьял Кола-апельсин газированная, 0,5 л, стекло</t>
+          <t>Зеленокумский Тархун, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>ООО ВПБЗ «Дарьял»</t>
+          <t>АО «Зеленокумский пивоваренный завод»</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Газированные напитки</t>
+          <t>Лимонады</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Кола-апельсин</t>
+          <t>Тархун</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -6626,7 +6429,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Дарьял Кола-апельсин — сильногазированный безалкогольный напиток со вкусом колы в стеклянной бутылке.</t>
+          <t>Газированный лимонад Зеленокумский со вкусом тархуна. Производство АО «Зеленокумский пивоваренный завод».</t>
         </is>
       </c>
       <c r="I9" s="5" t="n"/>
@@ -6635,22 +6438,22 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Дарьял Мохито газированная, 0,5 л, стекло</t>
+          <t>Зеленокумский Экстра-ситро, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>ООО ВПБЗ «Дарьял»</t>
+          <t>АО «Зеленокумский пивоваренный завод»</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Газированные напитки</t>
+          <t>Лимонады</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Мохито</t>
+          <t>Экстра-ситро</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -6665,88 +6468,10 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Дарьял Мохито — сильногазированный безалкогольный напиток со вкусом «Мохито» в стеклянной бутылке.</t>
+          <t>Газированный напиток Зеленокумский «Экстра-ситро» — цитрусовый вкус линейки завода.</t>
         </is>
       </c>
       <c r="I10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="96" customHeight="1">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Дарьял Тархун газированная, 0,5 л, стекло</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>ООО ВПБЗ «Дарьял»</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Тархун</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>0,5 л</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Дарьял Тархун — сильногазированный безалкогольный напиток со вкусом «Тархун» в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="96" customHeight="1">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Дарьял Фейхоа-Шелковица газированная, 0,5 л, стекло</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>ООО ВПБЗ «Дарьял»</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Газированные напитки</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Фейхоа-Шелковица</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>0,5 л</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>стекло</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>Дарьял Фейхоа-Шелковица — сильногазированный безалкогольный напиток со вкусом «Фейхоа-Шелковица» в стеклянной бутылке.</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6769,11 +6494,11 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -6781,7 +6506,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>ООО «Константа-7»</t>
+          <t>Нальчикский</t>
         </is>
       </c>
     </row>
@@ -6836,12 +6561,12 @@
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Барбарис, 0,5 л, стекло</t>
+          <t>Нальчикский Апельсиновый, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ООО «Константа-7»</t>
+          <t>ОАО «Халвичный завод «Нальчикский»»</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -6851,7 +6576,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Барбарис</t>
+          <t>Апельсиновый</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -6866,7 +6591,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Барбарис — сильногазированный безалкогольный напиток со вкусом «Барбарис» в стеклянной бутылке.</t>
+          <t>Сильногазированный напиток Халвичного завода «Нальчикский» со вкусом апельсина на артезианской воде.</t>
         </is>
       </c>
       <c r="I4" s="5" t="n"/>
@@ -6875,12 +6600,12 @@
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Груша, 0,5 л, стекло</t>
+          <t>Нальчикский Барбарис, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>ООО «Константа-7»</t>
+          <t>ОАО «Халвичный завод «Нальчикский»»</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -6890,7 +6615,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Груша</t>
+          <t>Барбарис</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -6905,7 +6630,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Груша — сильногазированный безалкогольный напиток со вкусом «Груша» в стеклянной бутылке.</t>
+          <t>Сильногазированный напиток «Барбарис» производства ОАО «Халвичный завод «Нальчикский»».</t>
         </is>
       </c>
       <c r="I5" s="5" t="n"/>
@@ -6914,12 +6639,12 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Дыня-Мята, 0,5 л, стекло</t>
+          <t>Нальчикский Белая черешня, 1,5 л, ПЭТ</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>ООО «Константа-7»</t>
+          <t>ОАО «Халвичный завод «Нальчикский»»</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -6929,22 +6654,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Дыня-Мята</t>
+          <t>Белая черешня</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>0,5 л</t>
+          <t>1,5 л</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>стекло</t>
+          <t>ПЭТ</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Дыня-Мята — сильногазированный безалкогольный напиток со вкусом «Дыня-Мята» в стеклянной бутылке.</t>
+          <t>Сильногазированный напиток «Белая черешня» от Халвичного завода «Нальчикский», ПЭТ 1,5 л.</t>
         </is>
       </c>
       <c r="I6" s="5" t="n"/>
@@ -6953,37 +6678,37 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Кола, 0,5 л, стекло</t>
+          <t>Нальчикский Вишневый, 1,5 л, ПЭТ</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>ООО «Константа-7»</t>
+          <t>ОАО «Халвичный завод «Нальчикский»»</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Кола</t>
+          <t>Лимонады</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Кола</t>
+          <t>Вишневый</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0,5 л</t>
+          <t>1,5 л</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>стекло</t>
+          <t>ПЭТ</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Кола — сильногазированный безалкогольный напиток со вкусом колы в стеклянной бутылке.</t>
+          <t>Сильногазированный напиток «Вишневый» Халвичного завода «Нальчикский», ПЭТ 1,5 л.</t>
         </is>
       </c>
       <c r="I7" s="5" t="n"/>
@@ -6992,12 +6717,12 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Лимонад, 0,5 л, стекло</t>
+          <t>Нальчикский Грушевый, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>ООО «Константа-7»</t>
+          <t>ОАО «Халвичный завод «Нальчикский»»</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -7007,7 +6732,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Лимонад</t>
+          <t>Грушевый</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -7022,7 +6747,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Лимонад — сильногазированный безалкогольный напиток со вкусом «Лимонад» в стеклянной бутылке.</t>
+          <t>Сильногазированный напиток «Грушевый» на артезианской воде собственного источника завода в Нальчике.</t>
         </is>
       </c>
       <c r="I8" s="5" t="n"/>
@@ -7031,12 +6756,12 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Манго-Виноград, 0,5 л, стекло</t>
+          <t>Нальчикский Лимонад, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>ООО «Константа-7»</t>
+          <t>ОАО «Халвичный завод «Нальчикский»»</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -7046,7 +6771,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Манго-Виноград</t>
+          <t>Лимонад</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -7061,7 +6786,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Манго-Виноград — сильногазированный безалкогольный напиток со вкусом «Манго-Виноград» в стеклянной бутылке.</t>
+          <t>Классический сильногазированный лимонад Халвичного завода «Нальчикский», стекло 0,5 л.</t>
         </is>
       </c>
       <c r="I9" s="5" t="n"/>
@@ -7070,12 +6795,12 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Саперави, 0,5 л, стекло</t>
+          <t>Нальчикский Мохито, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>ООО «Константа-7»</t>
+          <t>ОАО «Халвичный завод «Нальчикский»»</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -7085,7 +6810,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Саперави</t>
+          <t>Мохито</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -7100,7 +6825,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Саперави — сильногазированный безалкогольный напиток со вкусом «Саперави» в стеклянной бутылке.</t>
+          <t>Сильногазированный напиток «Мохито» производства ОАО «Халвичный завод «Нальчикский»».</t>
         </is>
       </c>
       <c r="I10" s="5" t="n"/>
@@ -7109,12 +6834,12 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Слива, 0,5 л, стекло</t>
+          <t>Нальчикский Тархун, 0,5 л, стекло</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>ООО «Константа-7»</t>
+          <t>ОАО «Халвичный завод «Нальчикский»»</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -7124,7 +6849,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Слива</t>
+          <t>Тархун</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -7139,7 +6864,7 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Слива — сильногазированный безалкогольный напиток со вкусом «Слива» в стеклянной бутылке.</t>
+          <t>Сильногазированный напиток «Тархун» Халвичного завода «Нальчикский» в стеклянной бутылке 0,5 л.</t>
         </is>
       </c>
       <c r="I11" s="5" t="n"/>
@@ -7148,12 +6873,12 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Тархун, 0,5 л, стекло</t>
+          <t>Нальчикский ТереКола, 1,5 л, ПЭТ</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>ООО «Константа-7»</t>
+          <t>ОАО «Халвичный завод «Нальчикский»»</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -7163,22 +6888,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Тархун</t>
+          <t>ТереКола</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>0,5 л</t>
+          <t>1,5 л</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>стекло</t>
+          <t>ПЭТ</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Тархун — сильногазированный безалкогольный напиток со вкусом «Тархун» в стеклянной бутылке.</t>
+          <t>Сильногазированный напиток «ТереКола» — фирменный колa-вкус линейки Халвичного завода «Нальчикский».</t>
         </is>
       </c>
       <c r="I12" s="5" t="n"/>
@@ -7187,12 +6912,12 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Фейхоа, 0,5 л, стекло</t>
+          <t>Нальчикский Экстра-ситро, 1,5 л, ПЭТ</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>ООО «Константа-7»</t>
+          <t>ОАО «Халвичный завод «Нальчикский»»</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -7202,22 +6927,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Фейхоа</t>
+          <t>Экстра-ситро</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0,5 л</t>
+          <t>1,5 л</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>стекло</t>
+          <t>ПЭТ</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Фейхоа — сильногазированный безалкогольный напиток со вкусом «Фейхоа» в стеклянной бутылке.</t>
+          <t>Сильногазированный напиток «Экстра-ситро» в ПЭТ 1,5 л от Халвичного завода «Нальчикский».</t>
         </is>
       </c>
       <c r="I13" s="5" t="n"/>
@@ -7226,12 +6951,12 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Напиток газированный AquAlania Игристое, 0,5 л, стекло</t>
+          <t>Нальчикский Яблочный, 1,5 л, ПЭТ</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>ООО «Константа-7»</t>
+          <t>ОАО «Халвичный завод «Нальчикский»»</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -7241,22 +6966,22 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Игристое</t>
+          <t>Яблочный</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>0,5 л</t>
+          <t>1,5 л</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>стекло</t>
+          <t>ПЭТ</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>AquAlania Игристое — сильногазированный безалкогольный напиток со вкусом «Игристое» в стеклянной бутылке.</t>
+          <t>Сильногазированный напиток «Яблочный» производства ОАО «Халвичный завод «Нальчикский»», ПЭТ 1,5 л.</t>
         </is>
       </c>
       <c r="I14" s="5" t="n"/>
@@ -7277,16 +7002,2370 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Фото</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Производитель</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Вкус</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Объём</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Тара</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Описание</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Цена</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="96" customHeight="1">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Вода минеральная Kazbek-Aqua, 0,33 л, стекло</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Минеральная вода</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Kazbek-Aqua</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>0,33 л</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Минеральная вода Kazbek-Aqua в стеклянной бутылке. Рекомендуется употреблять охлаждённой.</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="96" customHeight="1">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Вода питьевая TBAU Premium газированная, 0,33 л, стекло</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>TBAU Premium</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>0,33 л</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Газированная питьевая вода TBAU в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="96" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Вода питьевая TBAU Premium газированная, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>TBAU Premium</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Газированная питьевая вода TBAU в стеклянной бутылке, объёмом 0,45 л.</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="96" customHeight="1">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Вода питьевая TBAU Premium газированная, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>TBAU Premium</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Газированная питьевая вода TBAU в стеклянной бутылке, объёмом 0,5 л.</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="96" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Вода питьевая TBAU Premium негазированная, 0,33 л, стекло</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>TBAU Premium не</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>0,33 л</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Негазированная питьевая вода TBAU в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="96" customHeight="1">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Вода питьевая TBAU Premium негазированная, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>TBAU Premium не</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Негазированная питьевая вода TBAU в стеклянной бутылке, объёмом 0,45 л.</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="96" customHeight="1">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Вода питьевая TBAU Premium негазированная, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>TBAU Premium не</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Негазированная питьевая вода TBAU в стеклянной бутылке, объёмом 0,5 л.</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="96" customHeight="1">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Вода питьевая Аварал, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Аварал</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода Аварал в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="96" customHeight="1">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Вода питьевая Айва негазированная, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Айва</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Негазированная питьевая вода Айва в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="96" customHeight="1">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Вода питьевая Горная вода газированная, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Горная вода</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Газированная питьевая вода Горная вода в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="96" customHeight="1">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Вода питьевая Горная вода негазированная, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Питьевая вода</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Горная вода не</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Негазированная питьевая вода Горная вода в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="96" customHeight="1">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Cola Limited Edition газированная, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Cola Limited Edition</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Cola Limited Edition — сильногазированный безалкогольный напиток в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="96" customHeight="1">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный SWIPE газированная, 0,33 л, стекло</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>SWIPE</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>0,33 л</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>SWIPE — сильногазированный безалкогольный напиток в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="96" customHeight="1">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Premium Апельсин, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Апельсин</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Апельсин — сильногазированный безалкогольный напиток со вкусом «Апельсин» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="96" customHeight="1">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Premium Виноград, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Виноград</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Виноград — сильногазированный безалкогольный напиток со вкусом «Виноград» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="96" customHeight="1">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Premium Вишня, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Вишня</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Вишня — сильногазированный безалкогольный напиток со вкусом «Вишня» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="96" customHeight="1">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Premium Гранат, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Гранат</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Гранат — сильногазированный безалкогольный напиток со вкусом «Гранат» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="96" customHeight="1">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Premium Груша, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Груша</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Груша — сильногазированный безалкогольный напиток со вкусом «Груша» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="96" customHeight="1">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Premium Тархун, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Тархун</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Тархун — сильногазированный безалкогольный напиток со вкусом «Тархун» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="96" customHeight="1">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Premium Фейхоа, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Фейхоа</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Фейхоа — сильногазированный безалкогольный напиток со вкусом «Фейхоа» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="96" customHeight="1">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Груша, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Груша</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Груша — сильногазированный безалкогольный напиток со вкусом «Груша» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="96" customHeight="1">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Заповедная Тайга газированная, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Заповедная Тайга</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Заповедная Тайга — сильногазированный безалкогольный напиток со вкусом «Заповедная Тайга» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="96" customHeight="1">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Кола Premium LIMITED EDITION газированная, 0,33 л, стекло</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Кола Premium LIMITED EDITION</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>0,33 л</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Кола Premium LIMITED EDITION — сильногазированный безалкогольный напиток со вкусом колы в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="96" customHeight="1">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Кола Premium LIMITED EDITION газированная, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Кола Premium LIMITED EDITION</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Кола Premium LIMITED EDITION — сильногазированный безалкогольный напиток со вкусом колы в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="96" customHeight="1">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Мохито, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Мохито</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Мохито — сильногазированный безалкогольный напиток со вкусом «Мохито» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="96" customHeight="1">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Питахайя, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Питахайя</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Питахайя — сильногазированный безалкогольный напиток со вкусом «Питахайя» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="96" customHeight="1">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Родные Огоньки газированная, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Родные Огоньки</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Родные Огоньки — сильногазированный безалкогольный напиток со вкусом «Родные Огоньки» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="96" customHeight="1">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Тархун, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Тархун</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Тархун — сильногазированный безалкогольный напиток со вкусом «Тархун» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="96" customHeight="1">
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный Бавария Южная Чайка газированная, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Южная Чайка</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Южная Чайка — сильногазированный безалкогольный напиток со вкусом «Южная Чайка» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="96" customHeight="1">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Пиво безалкогольное Бавария Elf, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Безалкогольное пиво</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Elf</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Elf — безалкогольное пиво в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="96" customHeight="1">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Пиво безалкогольное Бавария Gallagher, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Безалкогольное пиво</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Gallagher</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Gallagher — безалкогольное пиво в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="96" customHeight="1">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Пиво безалкогольное Бавария Светлое, 0,45 л, стекло</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Безалкогольное пиво</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Светлое</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>0,45 л</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Бавария Светлое — безалкогольное пиво в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="n"/>
+    </row>
+    <row r="36" ht="96" customHeight="1">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Тоник Dreamix Bitter Lemon, 0,33 л, стекло</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Тоники</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Bitter Lemon</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>0,33 л</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Dreamix Bitter Lemon — безалкогольный тоник в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="96" customHeight="1">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Тоник Dreamix Indian Tonic, 0,33 л, стекло</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>ГК ПД «Бавария»</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Тоники</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Indian Tonic</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>0,33 л</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Dreamix Indian Tonic — безалкогольный тоник в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>ООО ВПБЗ «Дарьял»</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Фото</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Производитель</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Вкус</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Объём</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Тара</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Описание</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Цена</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="96" customHeight="1">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Аква Дарьял газированная, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>ООО ВПБЗ «Дарьял»</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Минеральная вода</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Газированная минеральная вода Аква Дарьял в стеклянной бутылке. Рекомендуется употреблять охлаждённой.</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="96" customHeight="1">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Аква Дарьял негазированная, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>ООО ВПБЗ «Дарьял»</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Минеральная вода</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>не</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Негазированная минеральная вода Аква Дарьял в стеклянной бутылке. Рекомендуется употреблять охлаждённой.</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="96" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Дарьял Апельсин-кориандр газированная, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>ООО ВПБЗ «Дарьял»</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Апельсин-кориандр</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Дарьял Апельсин-кориандр — сильногазированный безалкогольный напиток со вкусом «Апельсин-кориандр» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="96" customHeight="1">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Дарьял Гранат газированная, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>ООО ВПБЗ «Дарьял»</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Гранат</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Дарьял Гранат — сильногазированный безалкогольный напиток со вкусом «Гранат» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="96" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Дарьял Груша газированная, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>ООО ВПБЗ «Дарьял»</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Груша</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Дарьял Груша — сильногазированный безалкогольный напиток со вкусом «Груша» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="96" customHeight="1">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Дарьял Кола-апельсин газированная, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>ООО ВПБЗ «Дарьял»</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Кола-апельсин</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Дарьял Кола-апельсин — сильногазированный безалкогольный напиток со вкусом колы в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="96" customHeight="1">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Дарьял Мохито газированная, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>ООО ВПБЗ «Дарьял»</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Мохито</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Дарьял Мохито — сильногазированный безалкогольный напиток со вкусом «Мохито» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="96" customHeight="1">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Дарьял Тархун газированная, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>ООО ВПБЗ «Дарьял»</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Тархун</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Дарьял Тархун — сильногазированный безалкогольный напиток со вкусом «Тархун» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="96" customHeight="1">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Дарьял Фейхоа-Шелковица газированная, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>ООО ВПБЗ «Дарьял»</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Газированные напитки</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Фейхоа-Шелковица</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Дарьял Фейхоа-Шелковица — сильногазированный безалкогольный напиток со вкусом «Фейхоа-Шелковица» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Константа-7»</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Фото</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Производитель</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Вкус</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Объём</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Тара</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Описание</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Цена</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="96" customHeight="1">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Барбарис, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Константа-7»</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Лимонады</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Барбарис</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Барбарис — сильногазированный безалкогольный напиток со вкусом «Барбарис» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="96" customHeight="1">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Груша, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Константа-7»</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Лимонады</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Груша</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Груша — сильногазированный безалкогольный напиток со вкусом «Груша» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="96" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Дыня-Мята, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Константа-7»</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Лимонады</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Дыня-Мята</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Дыня-Мята — сильногазированный безалкогольный напиток со вкусом «Дыня-Мята» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="96" customHeight="1">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Кола, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Константа-7»</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Кола</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Кола</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Кола — сильногазированный безалкогольный напиток со вкусом колы в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="96" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Лимонад, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Константа-7»</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Лимонады</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Лимонад</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Лимонад — сильногазированный безалкогольный напиток со вкусом «Лимонад» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="96" customHeight="1">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Манго-Виноград, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Константа-7»</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Лимонады</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Манго-Виноград</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Манго-Виноград — сильногазированный безалкогольный напиток со вкусом «Манго-Виноград» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="96" customHeight="1">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Саперави, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Константа-7»</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Лимонады</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Саперави</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Саперави — сильногазированный безалкогольный напиток со вкусом «Саперави» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="96" customHeight="1">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Слива, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Константа-7»</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Лимонады</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Слива</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Слива — сильногазированный безалкогольный напиток со вкусом «Слива» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="96" customHeight="1">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Тархун, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Константа-7»</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Лимонады</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Тархун</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Тархун — сильногазированный безалкогольный напиток со вкусом «Тархун» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="96" customHeight="1">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Фейхоа, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Константа-7»</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Лимонады</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Фейхоа</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Фейхоа — сильногазированный безалкогольный напиток со вкусом «Фейхоа» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="96" customHeight="1">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Напиток газированный AquAlania Игристое, 0,5 л, стекло</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Константа-7»</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Лимонады</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Игристое</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>0,5 л</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>стекло</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>AquAlania Игристое — сильногазированный безалкогольный напиток со вкусом «Игристое» в стеклянной бутылке.</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -9272,10 +11351,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -9381,7 +11460,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9. ГК ПД «Бавария» (34)</t>
+          <t>9. От винта! (9)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -9391,36 +11470,63 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10. ООО ВПБЗ «Дарьял» (9)</t>
+          <t>10. Зеленокумский (7)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11. ООО «Константа-7» (11)</t>
+          <t>11. Нальчикский (11)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>12. ООО «ИРИБ» (49)</t>
+          <t>12. ГК ПД «Бавария» (34)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>13. ООО ВПБЗ «Дарьял» (9)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>14. ООО «Константа-7» (11)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>15. ООО «ИРИБ» (49)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>28</v>
+      </c>
+    </row>
     <row r="19"/>
     <row r="20"/>
     <row r="21"/>
@@ -9428,6 +11534,11 @@
     <row r="23"/>
     <row r="24"/>
     <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9444,11 +11555,11 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -9723,11 +11834,11 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -9885,11 +11996,11 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -10039,11 +12150,11 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -10158,11 +12269,11 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -10320,11 +12431,11 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -10911,11 +13022,11 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
